--- a/AAII_Financials/Yearly/OSK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OSK_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
   <si>
     <t>OSK</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44469</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44104</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43738</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43373</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43008</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42643</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42277</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41912</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41547</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41182</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40816</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9657900</v>
+      </c>
+      <c r="E8" s="3">
         <v>8282000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1791700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7737300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6856800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8382000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>7705500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6829600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6279200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6098100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6808200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7665100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8141100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7538500</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>7977100</v>
+      </c>
+      <c r="E9" s="3">
         <v>7227600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1620000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6511800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5732600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6864600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6349800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5648800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5223400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5058900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5625500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6471000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14324000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12931600</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1680800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1054400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>171700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1225500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1124200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1517400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1355700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1180800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1055800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1039200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1182700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1194100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-6182900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-5393100</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E14" s="3">
         <v>7700</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>14400</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>26900</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>11700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7800</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E15" s="3">
         <v>11600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>36900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>38300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>52500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>53200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>55300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>56600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>57700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>59300</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>8820300</v>
+      </c>
+      <c r="E17" s="3">
         <v>7909700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1773700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>7192600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6368100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7585000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7052000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>6359300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5915200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5699500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>6304900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7159400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7753400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7012400</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>837600</v>
+      </c>
+      <c r="E18" s="3">
         <v>372300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>544700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>488700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>797000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>653500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>470300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>364000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>398600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>503300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>505700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>387700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>526100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>28600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-43300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>8100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>12000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>3400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>5300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-3300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6200</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1026100</v>
+      </c>
+      <c r="E21" s="3">
         <v>436600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>650100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>602600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>920300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>786000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>601400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>496200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>520700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>630100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>637800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>515300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>676700</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E22" s="3">
         <v>53400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>48200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>59300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>54400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>70900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>59800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>60400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>70100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>71400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>66000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>75200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>90200</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>797600</v>
+      </c>
+      <c r="E23" s="3">
         <v>275600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>497900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>439100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>750700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>594600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>411300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>307000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>326100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>431900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>445000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>309200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>442100</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E24" s="3">
         <v>97500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-4400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>112800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>164300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>134500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>127200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>92400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>99200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>125000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>131700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>65200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>151600</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>607600</v>
+      </c>
+      <c r="E26" s="3">
         <v>178100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>5000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>472700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>326300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>586400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>460100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>284100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>214600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>226900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>306900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>313300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>244000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>290500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>598000</v>
+      </c>
+      <c r="E27" s="3">
         <v>173900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>472700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>324500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>586400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>461200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>285600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>216400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>229000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>308100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>314300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>244600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>290600</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1601,36 +1661,39 @@
       <c r="G29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3">
         <v>-7000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>10700</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>1700</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-14400</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-17600</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-28600</v>
+      </c>
+      <c r="E32" s="3">
         <v>43300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-8100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-12000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-3400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-5300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>3300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6200</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>598000</v>
+      </c>
+      <c r="E33" s="3">
         <v>173900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>472700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>324500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>579400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>471900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>285600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>216400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>229000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>308100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>316000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>230200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>273000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>598000</v>
+      </c>
+      <c r="E35" s="3">
         <v>173900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>472700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>324500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>579400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>471900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>285600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>216400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>229000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>308100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>316000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>230200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>273000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44469</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44104</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43738</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43373</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43008</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42643</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42277</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41912</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41547</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41182</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40816</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>125400</v>
+      </c>
+      <c r="E41" s="3">
         <v>805900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>995700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1375800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>582900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>448400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>454600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>447000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>321900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>42900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>313800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>733500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>540700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>428500</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2076,324 +2165,348 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2130200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1769900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1664500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1716500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1341200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1631800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1521600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1306300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1021900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>964600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>974900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>794300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1018600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1089100</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2131600</v>
+      </c>
+      <c r="E44" s="3">
         <v>1865600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1382700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1267400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1505400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1249200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1227700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1198400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>979800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1301700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>960900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>822000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>937500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>786800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E45" s="3">
         <v>90700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>71700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>58200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>106300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>78900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>66000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>88100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>93900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>142900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>134700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>203600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>197700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>150200</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4480800</v>
+      </c>
+      <c r="E46" s="3">
         <v>4532100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4114600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4417900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3535800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3408300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3269900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3039800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2417500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2377100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2384300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2553400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2694500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2454600</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>73700</v>
+      </c>
+      <c r="E47" s="3">
         <v>60800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>61000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>26200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>29200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>18900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>32600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>33900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>29900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>32500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>31600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>57700</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1333800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1063400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>593200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>812800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>728100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>573600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>481100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>469900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>452100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>475800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>405500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>362200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>369900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>388700</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2246600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1499000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1513000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1518800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1427700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1428000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1477300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1520800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1557000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1607800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1683400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1755700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1809200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1880200</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>994300</v>
+      </c>
+      <c r="E52" s="3">
         <v>573700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>492400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>81100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>98100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>127200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>47000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>53300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>76300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>83600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>61900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>42600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>45700</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9129200</v>
+      </c>
+      <c r="E54" s="3">
         <v>7729000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6721800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6891600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5815900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5566300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5294200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5098900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>4513800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4552700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4586700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4765700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4947800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4826900</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1214500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1129000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>747400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>860400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>577800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>795500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>776900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>651000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>466100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>552800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>586700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>531700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>683300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>768900</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>190400</v>
+      </c>
+      <c r="E58" s="3">
         <v>19600</v>
       </c>
-      <c r="E58" s="3">
-        <v>0</v>
-      </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>6900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8800</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>23000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>20000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>83500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>65000</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3">
         <v>40100</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1684700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1280000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1395600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1284400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>998500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>946400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>913200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1009100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>881500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>898700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>704900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>784000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1021200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>882800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3089600</v>
+      </c>
+      <c r="E60" s="3">
         <v>2428600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2143000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2151700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1585100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1741900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1690100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1683100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1367600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1458100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1311600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1380700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1704500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1691800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>641400</v>
+      </c>
+      <c r="E61" s="3">
         <v>613700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>819000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>834400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>827600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>819000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>818000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>807900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>826200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>844300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>875000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>890000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>955000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1020000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1692900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1501000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>683400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>657700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>552500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>405600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>272600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>300500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>343500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>339200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>415100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>387200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>434800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>518500</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5423900</v>
+      </c>
+      <c r="E66" s="3">
         <v>4543300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3645400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3643800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2965200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2966500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2780700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2791500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2537300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2641600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2601700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2657900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3094300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3230400</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3805800</v>
+      </c>
+      <c r="E72" s="3">
         <v>3315000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3110600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3129300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2747700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2505000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2007900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2399800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2177000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2016500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1840100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1581500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1263500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1032700</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3705300</v>
+      </c>
+      <c r="E76" s="3">
         <v>3185700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3076400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3247800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>2850700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2599800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2513500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2307400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1976500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1911100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1985000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2107800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1853500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1596500</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44469</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44104</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43738</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43373</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43008</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42643</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42277</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41912</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41547</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41182</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40816</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>598000</v>
+      </c>
+      <c r="E81" s="3">
         <v>173900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>472700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>324500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>579400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>471900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>285600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>216400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>229000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>308100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>316000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>230200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>273000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>159900</v>
+      </c>
+      <c r="E83" s="3">
         <v>107600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>104000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>104200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>115200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>120500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>130300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>128800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>124500</v>
-      </c>
-      <c r="M83" s="3">
-        <v>126800</v>
       </c>
       <c r="N83" s="3">
         <v>126800</v>
       </c>
       <c r="O83" s="3">
+        <v>126800</v>
+      </c>
+      <c r="P83" s="3">
         <v>130900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>144400</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>599600</v>
+      </c>
+      <c r="E89" s="3">
         <v>601300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-163100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1221600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>327300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>568300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>436300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>246500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>583900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>82500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>170400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>438000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>268300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>387700</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-325300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-279700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-43200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-114800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-130200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-174200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-100100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-113200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-127300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-158000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-124900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-59900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-64300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-86200</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1285600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-300400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-28700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-245600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-77600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-153000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-90400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-65200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-89200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-140100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-114800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-74800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-41800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-68300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-107200</v>
+      </c>
+      <c r="E96" s="3">
         <v>-97300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-24900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-90400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-81800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-75500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-71200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-62800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-55900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-53100</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-50700</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
       <c r="O96" s="3">
         <v>0</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-485000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-186300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-180400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-115500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-421600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-338900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-44800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-222000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-212900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-476000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-170000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-117300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-231500</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1600</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-680500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-189800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-380100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>792900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>134500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-6200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>125100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>279000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-270900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-419700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>192800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>112200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>89500</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/OSK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OSK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
   <si>
     <t>OSK</t>
   </si>
@@ -735,7 +735,7 @@
         <v>8282000</v>
       </c>
       <c r="F8" s="3">
-        <v>1791700</v>
+        <v>7952500</v>
       </c>
       <c r="G8" s="3">
         <v>7737300</v>
@@ -783,19 +783,19 @@
         <v>7227600</v>
       </c>
       <c r="F9" s="3">
-        <v>1620000</v>
+        <v>6779000</v>
       </c>
       <c r="G9" s="3">
-        <v>6511800</v>
+        <v>6469100</v>
       </c>
       <c r="H9" s="3">
-        <v>5732600</v>
+        <v>5751200</v>
       </c>
       <c r="I9" s="3">
         <v>6864600</v>
       </c>
       <c r="J9" s="3">
-        <v>6349800</v>
+        <v>6353500</v>
       </c>
       <c r="K9" s="3">
         <v>5648800</v>
@@ -831,19 +831,19 @@
         <v>1054400</v>
       </c>
       <c r="F10" s="3">
-        <v>171700</v>
+        <v>1173500</v>
       </c>
       <c r="G10" s="3">
-        <v>1225500</v>
+        <v>1268200</v>
       </c>
       <c r="H10" s="3">
-        <v>1124200</v>
+        <v>1105600</v>
       </c>
       <c r="I10" s="3">
         <v>1517400</v>
       </c>
       <c r="J10" s="3">
-        <v>1355700</v>
+        <v>1352000</v>
       </c>
       <c r="K10" s="3">
         <v>1180800</v>
@@ -892,26 +892,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>133600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>113400</v>
+      </c>
+      <c r="F12" s="3">
+        <v>25600</v>
+      </c>
+      <c r="G12" s="3">
+        <v>103100</v>
+      </c>
+      <c r="H12" s="3">
+        <v>103900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>99000</v>
+      </c>
+      <c r="J12" s="3">
+        <v>99300</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -989,25 +989,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>71500</v>
+        <v>35000</v>
       </c>
       <c r="E14" s="3">
-        <v>7700</v>
+        <v>28900</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>2800</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
-        <v>14400</v>
+        <v>-18500</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>-25600</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         <v>11600</v>
       </c>
       <c r="F15" s="3">
-        <v>2800</v>
+        <v>11100</v>
       </c>
       <c r="G15" s="3">
         <v>9600</v>
@@ -1102,25 +1102,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8820300</v>
+        <v>8804000</v>
       </c>
       <c r="E17" s="3">
-        <v>7909700</v>
+        <v>7901900</v>
       </c>
       <c r="F17" s="3">
-        <v>1773700</v>
+        <v>7464900</v>
       </c>
       <c r="G17" s="3">
-        <v>7192600</v>
+        <v>7149100</v>
       </c>
       <c r="H17" s="3">
-        <v>6368100</v>
+        <v>6420100</v>
       </c>
       <c r="I17" s="3">
-        <v>7585000</v>
+        <v>7587100</v>
       </c>
       <c r="J17" s="3">
-        <v>7052000</v>
+        <v>7077600</v>
       </c>
       <c r="K17" s="3">
         <v>6359300</v>
@@ -1150,25 +1150,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>837600</v>
+        <v>853900</v>
       </c>
       <c r="E18" s="3">
-        <v>372300</v>
+        <v>380100</v>
       </c>
       <c r="F18" s="3">
-        <v>18000</v>
+        <v>487600</v>
       </c>
       <c r="G18" s="3">
-        <v>544700</v>
+        <v>588200</v>
       </c>
       <c r="H18" s="3">
-        <v>488700</v>
+        <v>436700</v>
       </c>
       <c r="I18" s="3">
-        <v>797000</v>
+        <v>794900</v>
       </c>
       <c r="J18" s="3">
-        <v>653500</v>
+        <v>627900</v>
       </c>
       <c r="K18" s="3">
         <v>470300</v>
@@ -1218,25 +1218,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>28600</v>
+        <v>-22900</v>
       </c>
       <c r="E20" s="3">
-        <v>-43300</v>
+        <v>35900</v>
       </c>
       <c r="F20" s="3">
-        <v>-4900</v>
+        <v>1900</v>
       </c>
       <c r="G20" s="3">
-        <v>1400</v>
+        <v>-1800</v>
       </c>
       <c r="H20" s="3">
-        <v>9700</v>
+        <v>-30000</v>
       </c>
       <c r="I20" s="3">
-        <v>8100</v>
+        <v>-3400</v>
       </c>
       <c r="J20" s="3">
-        <v>12000</v>
+        <v>1500</v>
       </c>
       <c r="K20" s="3">
         <v>800</v>
@@ -1266,25 +1266,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1026100</v>
+        <v>909600</v>
       </c>
       <c r="E21" s="3">
-        <v>436600</v>
+        <v>355800</v>
       </c>
       <c r="F21" s="3">
-        <v>40100</v>
+        <v>496800</v>
       </c>
       <c r="G21" s="3">
-        <v>650100</v>
+        <v>599600</v>
       </c>
       <c r="H21" s="3">
-        <v>602600</v>
+        <v>477700</v>
       </c>
       <c r="I21" s="3">
-        <v>920300</v>
+        <v>835200</v>
       </c>
       <c r="J21" s="3">
-        <v>786000</v>
+        <v>664700</v>
       </c>
       <c r="K21" s="3">
         <v>601400</v>
@@ -1332,7 +1332,7 @@
         <v>54400</v>
       </c>
       <c r="J22" s="3">
-        <v>70900</v>
+        <v>71600</v>
       </c>
       <c r="K22" s="3">
         <v>59800</v>
@@ -1362,25 +1362,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>797600</v>
+        <v>788000</v>
       </c>
       <c r="E23" s="3">
-        <v>275600</v>
+        <v>271400</v>
       </c>
       <c r="F23" s="3">
-        <v>600</v>
+        <v>440600</v>
       </c>
       <c r="G23" s="3">
-        <v>497900</v>
+        <v>545300</v>
       </c>
       <c r="H23" s="3">
-        <v>439100</v>
+        <v>433400</v>
       </c>
       <c r="I23" s="3">
         <v>750700</v>
       </c>
       <c r="J23" s="3">
-        <v>594600</v>
+        <v>595700</v>
       </c>
       <c r="K23" s="3">
         <v>411300</v>
@@ -1416,19 +1416,19 @@
         <v>97500</v>
       </c>
       <c r="F24" s="3">
-        <v>-4400</v>
+        <v>13200</v>
       </c>
       <c r="G24" s="3">
-        <v>25200</v>
+        <v>36400</v>
       </c>
       <c r="H24" s="3">
-        <v>112800</v>
+        <v>111900</v>
       </c>
       <c r="I24" s="3">
-        <v>164300</v>
+        <v>171300</v>
       </c>
       <c r="J24" s="3">
-        <v>134500</v>
+        <v>123800</v>
       </c>
       <c r="K24" s="3">
         <v>127200</v>
@@ -1506,25 +1506,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>607600</v>
+        <v>598000</v>
       </c>
       <c r="E26" s="3">
-        <v>178100</v>
+        <v>173900</v>
       </c>
       <c r="F26" s="3">
-        <v>5000</v>
+        <v>427400</v>
       </c>
       <c r="G26" s="3">
-        <v>472700</v>
+        <v>508900</v>
       </c>
       <c r="H26" s="3">
-        <v>326300</v>
+        <v>321500</v>
       </c>
       <c r="I26" s="3">
-        <v>586400</v>
+        <v>579400</v>
       </c>
       <c r="J26" s="3">
-        <v>460100</v>
+        <v>471900</v>
       </c>
       <c r="K26" s="3">
         <v>284100</v>
@@ -1560,19 +1560,19 @@
         <v>173900</v>
       </c>
       <c r="F27" s="3">
-        <v>6200</v>
+        <v>427400</v>
       </c>
       <c r="G27" s="3">
-        <v>472700</v>
+        <v>508900</v>
       </c>
       <c r="H27" s="3">
-        <v>324500</v>
+        <v>321500</v>
       </c>
       <c r="I27" s="3">
-        <v>586400</v>
+        <v>579400</v>
       </c>
       <c r="J27" s="3">
-        <v>461200</v>
+        <v>471900</v>
       </c>
       <c r="K27" s="3">
         <v>285600</v>
@@ -1649,26 +1649,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-7000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>10700</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1794,25 +1794,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-28600</v>
+        <v>22900</v>
       </c>
       <c r="E32" s="3">
-        <v>43300</v>
+        <v>-35900</v>
       </c>
       <c r="F32" s="3">
-        <v>4900</v>
+        <v>-1900</v>
       </c>
       <c r="G32" s="3">
-        <v>-1400</v>
+        <v>1800</v>
       </c>
       <c r="H32" s="3">
-        <v>-9700</v>
+        <v>30000</v>
       </c>
       <c r="I32" s="3">
-        <v>-8100</v>
+        <v>3400</v>
       </c>
       <c r="J32" s="3">
-        <v>-12000</v>
+        <v>-1500</v>
       </c>
       <c r="K32" s="3">
         <v>-800</v>
@@ -1848,13 +1848,13 @@
         <v>173900</v>
       </c>
       <c r="F33" s="3">
-        <v>6200</v>
+        <v>427400</v>
       </c>
       <c r="G33" s="3">
-        <v>472700</v>
+        <v>508900</v>
       </c>
       <c r="H33" s="3">
-        <v>324500</v>
+        <v>321500</v>
       </c>
       <c r="I33" s="3">
         <v>579400</v>
@@ -1944,13 +1944,13 @@
         <v>173900</v>
       </c>
       <c r="F35" s="3">
-        <v>6200</v>
+        <v>427400</v>
       </c>
       <c r="G35" s="3">
-        <v>472700</v>
+        <v>508900</v>
       </c>
       <c r="H35" s="3">
-        <v>324500</v>
+        <v>321500</v>
       </c>
       <c r="I35" s="3">
         <v>579400</v>
@@ -2187,7 +2187,7 @@
         <v>1716500</v>
       </c>
       <c r="H43" s="3">
-        <v>1341200</v>
+        <v>1386600</v>
       </c>
       <c r="I43" s="3">
         <v>1631800</v>
@@ -2229,10 +2229,10 @@
         <v>1865600</v>
       </c>
       <c r="F44" s="3">
-        <v>1382700</v>
+        <v>1550400</v>
       </c>
       <c r="G44" s="3">
-        <v>1267400</v>
+        <v>1411500</v>
       </c>
       <c r="H44" s="3">
         <v>1505400</v>
@@ -2283,7 +2283,7 @@
         <v>58200</v>
       </c>
       <c r="H45" s="3">
-        <v>106300</v>
+        <v>60900</v>
       </c>
       <c r="I45" s="3">
         <v>78900</v>
@@ -2325,10 +2325,10 @@
         <v>4532100</v>
       </c>
       <c r="F46" s="3">
-        <v>4114600</v>
+        <v>4282300</v>
       </c>
       <c r="G46" s="3">
-        <v>4417900</v>
+        <v>4562000</v>
       </c>
       <c r="H46" s="3">
         <v>3535800</v>
@@ -2367,25 +2367,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>73700</v>
+        <v>43300</v>
       </c>
       <c r="E47" s="3">
-        <v>60800</v>
+        <v>50700</v>
       </c>
       <c r="F47" s="3">
-        <v>8600</v>
+        <v>46800</v>
       </c>
       <c r="G47" s="3">
-        <v>61000</v>
+        <v>51200</v>
       </c>
       <c r="H47" s="3">
-        <v>26200</v>
+        <v>12600</v>
       </c>
       <c r="I47" s="3">
-        <v>29200</v>
+        <v>11000</v>
       </c>
       <c r="J47" s="3">
-        <v>18900</v>
+        <v>12900</v>
       </c>
       <c r="K47" s="3">
         <v>32600</v>
@@ -2418,10 +2418,10 @@
         <v>1333800</v>
       </c>
       <c r="E48" s="3">
-        <v>1063400</v>
+        <v>1063300</v>
       </c>
       <c r="F48" s="3">
-        <v>593200</v>
+        <v>827300</v>
       </c>
       <c r="G48" s="3">
         <v>812800</v>
@@ -2607,25 +2607,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>994300</v>
+        <v>37300</v>
       </c>
       <c r="E52" s="3">
-        <v>573700</v>
+        <v>29900</v>
       </c>
       <c r="F52" s="3">
-        <v>492400</v>
+        <v>32100</v>
       </c>
       <c r="G52" s="3">
-        <v>81100</v>
+        <v>29700</v>
       </c>
       <c r="H52" s="3">
-        <v>98100</v>
+        <v>28000</v>
       </c>
       <c r="I52" s="3">
-        <v>127200</v>
+        <v>30700</v>
       </c>
       <c r="J52" s="3">
-        <v>47000</v>
+        <v>37400</v>
       </c>
       <c r="K52" s="3">
         <v>35800</v>
@@ -2709,10 +2709,10 @@
         <v>7729000</v>
       </c>
       <c r="F54" s="3">
-        <v>6721800</v>
+        <v>6849700</v>
       </c>
       <c r="G54" s="3">
-        <v>6891600</v>
+        <v>7035700</v>
       </c>
       <c r="H54" s="3">
         <v>5815900</v>
@@ -2839,19 +2839,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>190400</v>
+        <v>229000</v>
       </c>
       <c r="E58" s="3">
-        <v>19600</v>
+        <v>64200</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>51100</v>
       </c>
       <c r="G58" s="3">
-        <v>6900</v>
+        <v>46200</v>
       </c>
       <c r="H58" s="3">
-        <v>8800</v>
+        <v>52300</v>
       </c>
       <c r="I58" s="3">
         <v>0</v>
@@ -2887,25 +2887,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1684700</v>
+        <v>1403600</v>
       </c>
       <c r="E59" s="3">
-        <v>1280000</v>
+        <v>1115900</v>
       </c>
       <c r="F59" s="3">
-        <v>1395600</v>
+        <v>1226100</v>
       </c>
       <c r="G59" s="3">
-        <v>1284400</v>
+        <v>1030000</v>
       </c>
       <c r="H59" s="3">
-        <v>998500</v>
+        <v>804200</v>
       </c>
       <c r="I59" s="3">
-        <v>946400</v>
+        <v>762800</v>
       </c>
       <c r="J59" s="3">
-        <v>913200</v>
+        <v>720700</v>
       </c>
       <c r="K59" s="3">
         <v>1009100</v>
@@ -2983,19 +2983,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>641400</v>
+        <v>819500</v>
       </c>
       <c r="E61" s="3">
-        <v>613700</v>
+        <v>788400</v>
       </c>
       <c r="F61" s="3">
-        <v>819000</v>
+        <v>1009200</v>
       </c>
       <c r="G61" s="3">
-        <v>834400</v>
+        <v>995200</v>
       </c>
       <c r="H61" s="3">
-        <v>827600</v>
+        <v>936700</v>
       </c>
       <c r="I61" s="3">
         <v>819000</v>
@@ -3031,25 +3031,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1692900</v>
+        <v>228800</v>
       </c>
       <c r="E62" s="3">
-        <v>1501000</v>
+        <v>239000</v>
       </c>
       <c r="F62" s="3">
-        <v>683400</v>
+        <v>231300</v>
       </c>
       <c r="G62" s="3">
-        <v>657700</v>
+        <v>355900</v>
       </c>
       <c r="H62" s="3">
-        <v>552500</v>
+        <v>164500</v>
       </c>
       <c r="I62" s="3">
-        <v>405600</v>
+        <v>167300</v>
       </c>
       <c r="J62" s="3">
-        <v>272600</v>
+        <v>119700</v>
       </c>
       <c r="K62" s="3">
         <v>300500</v>
@@ -3232,7 +3232,7 @@
         <v>3645400</v>
       </c>
       <c r="G66" s="3">
-        <v>3643800</v>
+        <v>3678000</v>
       </c>
       <c r="H66" s="3">
         <v>2965200</v>
@@ -3489,10 +3489,10 @@
         <v>3315000</v>
       </c>
       <c r="F72" s="3">
-        <v>3110600</v>
+        <v>3238500</v>
       </c>
       <c r="G72" s="3">
-        <v>3129300</v>
+        <v>3239200</v>
       </c>
       <c r="H72" s="3">
         <v>2747700</v>
@@ -3681,10 +3681,10 @@
         <v>3185700</v>
       </c>
       <c r="F76" s="3">
-        <v>3076400</v>
+        <v>3204300</v>
       </c>
       <c r="G76" s="3">
-        <v>3247800</v>
+        <v>3357700</v>
       </c>
       <c r="H76" s="3">
         <v>2850700</v>
@@ -3830,13 +3830,13 @@
         <v>173900</v>
       </c>
       <c r="F81" s="3">
-        <v>6200</v>
+        <v>427400</v>
       </c>
       <c r="G81" s="3">
-        <v>472700</v>
+        <v>508900</v>
       </c>
       <c r="H81" s="3">
-        <v>324500</v>
+        <v>321500</v>
       </c>
       <c r="I81" s="3">
         <v>579400</v>
@@ -3892,25 +3892,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>159900</v>
+        <v>118200</v>
       </c>
       <c r="E83" s="3">
-        <v>107600</v>
+        <v>96000</v>
       </c>
       <c r="F83" s="3">
-        <v>27000</v>
+        <v>92500</v>
       </c>
       <c r="G83" s="3">
-        <v>104000</v>
+        <v>90800</v>
       </c>
       <c r="H83" s="3">
-        <v>104200</v>
+        <v>86300</v>
       </c>
       <c r="I83" s="3">
-        <v>115200</v>
+        <v>76700</v>
       </c>
       <c r="J83" s="3">
-        <v>120500</v>
+        <v>79800</v>
       </c>
       <c r="K83" s="3">
         <v>130300</v>
@@ -4186,7 +4186,7 @@
         <v>601300</v>
       </c>
       <c r="F89" s="3">
-        <v>-163100</v>
+        <v>690400</v>
       </c>
       <c r="G89" s="3">
         <v>1221600</v>
@@ -4251,13 +4251,13 @@
         <v>-325300</v>
       </c>
       <c r="E91" s="3">
-        <v>-279700</v>
+        <v>-269500</v>
       </c>
       <c r="F91" s="3">
-        <v>-43200</v>
+        <v>-39400</v>
       </c>
       <c r="G91" s="3">
-        <v>-114800</v>
+        <v>-104400</v>
       </c>
       <c r="H91" s="3">
         <v>-130200</v>
@@ -4460,25 +4460,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-107200</v>
+        <v>107200</v>
       </c>
       <c r="E96" s="3">
-        <v>-97300</v>
+        <v>97300</v>
       </c>
       <c r="F96" s="3">
-        <v>-24900</v>
+        <v>24900</v>
       </c>
       <c r="G96" s="3">
-        <v>-90400</v>
+        <v>90400</v>
       </c>
       <c r="H96" s="3">
-        <v>-81800</v>
+        <v>81800</v>
       </c>
       <c r="I96" s="3">
-        <v>-75500</v>
+        <v>75500</v>
       </c>
       <c r="J96" s="3">
-        <v>-71200</v>
+        <v>71200</v>
       </c>
       <c r="K96" s="3">
         <v>-62800</v>
@@ -4754,7 +4754,7 @@
         <v>-189800</v>
       </c>
       <c r="F102" s="3">
-        <v>-380100</v>
+        <v>473400</v>
       </c>
       <c r="G102" s="3">
         <v>792900</v>

--- a/AAII_Financials/Yearly/OSK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OSK_YR_FIN.xlsx
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44469</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44104</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43738</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43373</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43008</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42643</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42277</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41912</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41547</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41182</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40816</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10730200</v>
+      </c>
+      <c r="E8" s="3">
         <v>9657900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>8282000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>7952500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7737300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6856800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8382000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>7705500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6829600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6279200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6098100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6808200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7665100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>8141100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>7538500</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8760800</v>
+      </c>
+      <c r="E9" s="3">
         <v>7977100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7227600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6779000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6469100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5751200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>6864600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6353500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5648800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5223400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5058900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5625500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6471000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14324000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12931600</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1969400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1680800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1054400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1173500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1268200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1105600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1517400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1352000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1180800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1055800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1039200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1182700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1194100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-6182900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-5393100</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,34 +899,35 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>169100</v>
+      </c>
+      <c r="E12" s="3">
         <v>133600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>113400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>103100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>103900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>99000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>99300</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -934,9 +947,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>35000</v>
+        <v>72500</v>
       </c>
       <c r="E14" s="3">
-        <v>28900</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+        <v>34400</v>
+      </c>
+      <c r="F14" s="3">
+        <v>7700</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3">
         <v>-18500</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-25600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>26900</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>11700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7800</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>54700</v>
+      </c>
+      <c r="E15" s="3">
         <v>32800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>11600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>11000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>36900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>38300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>52500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>53200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>55300</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>56600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>57700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>59300</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>8804000</v>
+        <v>9663000</v>
       </c>
       <c r="E17" s="3">
-        <v>7901900</v>
+        <v>8804600</v>
       </c>
       <c r="F17" s="3">
+        <v>7935500</v>
+      </c>
+      <c r="G17" s="3">
         <v>7464900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7149100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>6420100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>7587100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7077600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6359300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5915200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5699500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>6304900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7159400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7753400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7012400</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>853900</v>
+        <v>1067200</v>
       </c>
       <c r="E18" s="3">
-        <v>380100</v>
+        <v>853300</v>
       </c>
       <c r="F18" s="3">
+        <v>346500</v>
+      </c>
+      <c r="G18" s="3">
         <v>487600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>588200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>436700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>794900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>627900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>470300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>364000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>398600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>503300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>505700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>387700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>526100</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1212,248 +1244,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-8600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-22900</v>
       </c>
-      <c r="E20" s="3">
-        <v>35900</v>
-      </c>
       <c r="F20" s="3">
+        <v>23500</v>
+      </c>
+      <c r="G20" s="3">
         <v>1900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-30000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2400</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>5300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6200</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>909600</v>
+        <v>1130500</v>
       </c>
       <c r="E21" s="3">
-        <v>355800</v>
+        <v>909000</v>
       </c>
       <c r="F21" s="3">
+        <v>334600</v>
+      </c>
+      <c r="G21" s="3">
         <v>496800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>599600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>477700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>835200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>664700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>601400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>496200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>520700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>630100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>637800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>515300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>676700</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>119500</v>
+      </c>
+      <c r="E22" s="3">
         <v>68600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>53400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>48200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>59300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>54400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>71600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>59800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>60400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>70100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>71400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>66000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>75200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>90200</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>891400</v>
+      </c>
+      <c r="E23" s="3">
         <v>788000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>271400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>440600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>545300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>433400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>750700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>595700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>411300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>307000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>326100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>431900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>445000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>309200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>442100</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E24" s="3">
         <v>190000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>97500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>36400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>111900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>171300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>123800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>127200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>92400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>99200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>125000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>131700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>65200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>151600</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>681400</v>
+      </c>
+      <c r="E26" s="3">
         <v>598000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>173900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>427400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>508900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>321500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>579400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>471900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>284100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>214600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>226900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>306900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>313300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>244000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>290500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>681400</v>
+      </c>
+      <c r="E27" s="3">
         <v>598000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>173900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>427400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>508900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>321500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>579400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>471900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>285600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>216400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>229000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>308100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>314300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>244600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>290600</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1670,30 +1730,33 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>1700</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-14400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-17600</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E32" s="3">
         <v>22900</v>
       </c>
-      <c r="E32" s="3">
-        <v>-35900</v>
-      </c>
       <c r="F32" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>30000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2400</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-5300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>3300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6200</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>681400</v>
+      </c>
+      <c r="E33" s="3">
         <v>598000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>173900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>427400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>508900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>321500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>579400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>471900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>285600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>216400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>229000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>308100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>316000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>230200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>273000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>681400</v>
+      </c>
+      <c r="E35" s="3">
         <v>598000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>173900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>427400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>508900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>321500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>579400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>471900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>285600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>216400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>229000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>308100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>316000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>230200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>273000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44469</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44104</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43738</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43373</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43008</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42643</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42277</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41912</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41547</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41182</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40816</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>204900</v>
+      </c>
+      <c r="E41" s="3">
         <v>125400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>805900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>995700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1375800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>582900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>448400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>454600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>447000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>321900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>42900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>313800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>733500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>540700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>428500</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2168,345 +2257,369 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1942400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2130200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1769900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1664500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1716500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1386600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1631800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1521600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1306300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1021900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>964600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>974900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>794300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1018600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1089100</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2265700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2131600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1865600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1550400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1411500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1505400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1249200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1227700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1198400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>979800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1301700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>960900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>822000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>937500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>786800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>114500</v>
+      </c>
+      <c r="E45" s="3">
         <v>93600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>90700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>71700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>58200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>60900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>78900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>66000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>88100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>93900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>142900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>134700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>203600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>197700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>150200</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4527500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4480800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4532100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4282300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4562000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3535800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3408300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3269900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3039800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2417500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2377100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2384300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2553400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2694500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2454600</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E47" s="3">
         <v>43300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>50700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>46800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>51200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>12600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>11000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>12900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>32600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>33900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>32400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>29900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>32500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>31600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>57700</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1473800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1333800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1063300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>827300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>812800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>728100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>573600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>481100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>469900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>452100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>475800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>405500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>362200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>369900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>388700</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2187700</v>
+      </c>
+      <c r="E49" s="3">
         <v>2246600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1499000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1513000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1518800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1427700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1428000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1477300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1520800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1557000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1607800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1683400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1755700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1809200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1880200</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>37300</v>
+        <v>94100</v>
       </c>
       <c r="E52" s="3">
+        <v>52000</v>
+      </c>
+      <c r="F52" s="3">
         <v>29900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>32100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>29700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>28000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>30700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>37400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>53300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>76300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>83600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>61900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>42600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>45700</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9423100</v>
+      </c>
+      <c r="E54" s="3">
         <v>9129200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>7729000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6849700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7035700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>5815900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5566300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5294200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5098900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>4513800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4552700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4586700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4765700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4947800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4826900</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,296 +2914,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1143400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1214500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1129000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>747400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>860400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>577800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>795500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>776900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>651000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>466100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>552800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>586700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>531700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>683300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>768900</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>419000</v>
+      </c>
+      <c r="E58" s="3">
         <v>229000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>64200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>51100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>46200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>52300</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>23000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>20000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>83500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>20000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>65000</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
         <v>40100</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1178700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1403600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1115900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1226100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1030000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>804200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>762800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>720700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1009100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>881500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>898700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>704900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>784000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1021200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>882800</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2987300</v>
+      </c>
+      <c r="E60" s="3">
         <v>3089600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2428600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2143000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2151700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1585100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1741900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1690100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1683100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1367600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1458100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1311600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1380700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1704500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1691800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>809300</v>
+      </c>
+      <c r="E61" s="3">
         <v>819500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>788400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1009200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>995200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>936700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>819000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>818000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>807900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>826200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>844300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>875000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>890000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>955000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1020000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>220400</v>
+      </c>
+      <c r="E62" s="3">
         <v>228800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>239000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>231300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>355900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>164500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>167300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>119700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>300500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>343500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>339200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>415100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>387200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>434800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>518500</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5271000</v>
+      </c>
+      <c r="E66" s="3">
         <v>5423900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4543300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3645400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3678000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2965200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2966500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2780700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2791500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2537300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2641600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2601700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2657900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3094300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3230400</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3428,9 +3595,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,57 +3646,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4367200</v>
+      </c>
+      <c r="E72" s="3">
         <v>3805800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3315000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3238500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3239200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2747700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2505000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2007900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2399800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2177000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2016500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1840100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1581500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1263500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1032700</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4152100</v>
+      </c>
+      <c r="E76" s="3">
         <v>3705300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3185700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3204300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3357700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>2850700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2599800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2513500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2307400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1976500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1911100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1985000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2107800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1853500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1596500</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44469</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44104</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43738</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43373</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43008</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42643</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42277</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41912</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41547</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41182</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40816</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>681400</v>
+      </c>
+      <c r="E81" s="3">
         <v>598000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>173900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>427400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>508900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>321500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>579400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>471900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>285600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>216400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>229000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>308100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>316000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>230200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>273000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>135200</v>
+      </c>
+      <c r="E83" s="3">
         <v>118200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>96000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>92500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>90800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>86300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>76700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>79800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>130300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>128800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>124500</v>
-      </c>
-      <c r="N83" s="3">
-        <v>126800</v>
       </c>
       <c r="O83" s="3">
         <v>126800</v>
       </c>
       <c r="P83" s="3">
+        <v>126800</v>
+      </c>
+      <c r="Q83" s="3">
         <v>130900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>144400</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>550100</v>
+      </c>
+      <c r="E89" s="3">
         <v>599600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>601300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>690400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1221600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>327300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>568300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>436300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>246500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>583900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>82500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>170400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>438000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>268300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>387700</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-281000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-325300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-269500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-39400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-104400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-130200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-174200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-100100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-113200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-127300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-158000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-124900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-59900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-86200</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-388800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1285600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-300400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-28700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-245600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-77600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-153000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-90400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-65200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-89200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-140100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-114800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-74800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-41800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-68300</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,56 +4686,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E96" s="3">
         <v>107200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>97300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>24900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>90400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>81800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>75500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>71200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-62800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-55900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-53100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-50700</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
-      </c>
       <c r="P96" s="3">
         <v>0</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,151 +4887,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-75100</v>
+      </c>
+      <c r="E100" s="3">
         <v>3400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-485000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-186300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-180400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-115500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-421600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-338900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-44800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-222000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-212900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-476000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-170000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-117300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-231500</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="E101" s="3">
         <v>2100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2700</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1600</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-680500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-189800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>473400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>792900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>134500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>125100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>279000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-270900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-419700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>192800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>112200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>89500</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/OSK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OSK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
   <si>
     <t>OSK</t>
   </si>
@@ -656,231 +656,243 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44104</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43738</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43373</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43008</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42643</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42277</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41912</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41547</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>41182</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>40816</v>
       </c>
-      <c r="S7" s="2"/>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T7" s="2"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10422300</v>
+      </c>
+      <c r="E8" s="3">
         <v>10730200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9657900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8282000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7952500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7737300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6856800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8382000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7705500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6829600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6279200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6098100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>6808200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7665100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>8141100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>7538500</v>
       </c>
-      <c r="S8" s="3"/>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T8" s="3"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>8603300</v>
+      </c>
+      <c r="E9" s="3">
         <v>8760800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>7977100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>7227600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6779000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>6469100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5751200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6864600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6353500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5648800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5223400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5058900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5625500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>6471000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14324000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12931600</v>
       </c>
-      <c r="S9" s="3"/>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T9" s="3"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1819000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1969400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1680800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1054400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1173500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1268200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1105600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1517400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1352000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1180800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1055800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1039200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1182700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1194100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-6182900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-5393100</v>
       </c>
-      <c r="S10" s="3"/>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T10" s="3"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -900,37 +912,38 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>173700</v>
+      </c>
+      <c r="E12" s="3">
         <v>169100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>133600</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>113400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>25600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>103100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>103900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>99000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>99300</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -950,9 +963,12 @@
       <c r="R12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S12" s="3"/>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1001,111 +1017,120 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-      <c r="S13" s="3"/>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>72500</v>
+        <v>19700</v>
       </c>
       <c r="E14" s="3">
-        <v>34400</v>
-      </c>
-      <c r="F14" s="3">
+        <v>71400</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>7700</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>-18500</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-25600</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>26900</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>11700</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7800</v>
       </c>
-      <c r="S14" s="3"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>55100</v>
+      </c>
+      <c r="E15" s="3">
         <v>54700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>32800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>11600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>11100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>11000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>36900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>38300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>52500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>53200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>55300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>56600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>57700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>59300</v>
       </c>
-      <c r="S15" s="3"/>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1122,110 +1147,117 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>9663000</v>
+        <v>9470100</v>
       </c>
       <c r="E17" s="3">
-        <v>8804600</v>
+        <v>9664100</v>
       </c>
       <c r="F17" s="3">
+        <v>8817500</v>
+      </c>
+      <c r="G17" s="3">
         <v>7935500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>7464900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>7149100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>6420100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>7587100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7077600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>6359300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5915200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5699500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>6304900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7159400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>7753400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>7012400</v>
       </c>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1067200</v>
+        <v>952200</v>
       </c>
       <c r="E18" s="3">
-        <v>853300</v>
+        <v>1066100</v>
       </c>
       <c r="F18" s="3">
+        <v>840400</v>
+      </c>
+      <c r="G18" s="3">
         <v>346500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>487600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>588200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>436700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>794900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>627900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>470300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>364000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>398600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>503300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>505700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>387700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>526100</v>
       </c>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1245,263 +1277,279 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-14900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-8600</v>
       </c>
-      <c r="E20" s="3">
-        <v>-22900</v>
-      </c>
       <c r="F20" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="G20" s="3">
         <v>23500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-30000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2400</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>5300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-3300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6200</v>
       </c>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1130500</v>
+        <v>1022200</v>
       </c>
       <c r="E21" s="3">
-        <v>909000</v>
+        <v>1129400</v>
       </c>
       <c r="F21" s="3">
+        <v>874600</v>
+      </c>
+      <c r="G21" s="3">
         <v>334600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>496800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>599600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>477700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>835200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>664700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>601400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>496200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>520700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>630100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>637800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>515300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>676700</v>
       </c>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>117600</v>
+      </c>
+      <c r="E22" s="3">
         <v>119500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>68600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>53400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>48200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>59300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>54400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>71600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>59800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>60400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>70100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>71400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>66000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>75200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>90200</v>
       </c>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>838500</v>
+      </c>
+      <c r="E23" s="3">
         <v>891400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>788000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>271400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>440600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>545300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>433400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>750700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>595700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>411300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>307000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>326100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>431900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>445000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>309200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>442100</v>
       </c>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T23" s="3"/>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>191500</v>
+      </c>
+      <c r="E24" s="3">
         <v>210000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>190000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>97500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>36400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>111900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>171300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>123800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>127200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>92400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>99200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>125000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>131700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>65200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>151600</v>
       </c>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T24" s="3"/>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1550,111 +1598,120 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3"/>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E26" s="3">
         <v>681400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>598000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>173900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>427400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>508900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>321500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>579400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>471900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>284100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>214600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>226900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>306900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>313300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>244000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>290500</v>
       </c>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T26" s="3"/>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E27" s="3">
         <v>681400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>598000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>173900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>427400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>508900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>321500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>579400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>471900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>285600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>216400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>229000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>308100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>314300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>244600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>290600</v>
       </c>
-      <c r="S27" s="3"/>
-    </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T27" s="3"/>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1703,9 +1760,12 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3"/>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1733,30 +1793,33 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
       </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>1700</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-14400</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-17600</v>
       </c>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3"/>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1805,9 +1868,12 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3"/>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1856,111 +1922,120 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3"/>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E32" s="3">
         <v>8600</v>
       </c>
-      <c r="E32" s="3">
-        <v>22900</v>
-      </c>
       <c r="F32" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G32" s="3">
         <v>-23500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>30000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2400</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>3300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6200</v>
       </c>
-      <c r="S32" s="3"/>
-    </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T32" s="3"/>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E33" s="3">
         <v>681400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>598000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>173900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>427400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>508900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>321500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>579400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>471900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>285600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>216400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>229000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>308100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>316000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>230200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>273000</v>
       </c>
-      <c r="S33" s="3"/>
-    </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T33" s="3"/>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2009,116 +2084,125 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-      <c r="S34" s="3"/>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3"/>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E35" s="3">
         <v>681400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>598000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>173900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>427400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>508900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>321500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>579400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>471900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>285600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>216400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>229000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>308100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>316000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>230200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>273000</v>
       </c>
-      <c r="S35" s="3"/>
-    </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T35" s="3"/>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44104</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43738</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43373</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43008</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42643</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42277</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41912</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41547</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>41182</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>40816</v>
       </c>
-      <c r="S38" s="2"/>
-    </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T38" s="2"/>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2138,8 +2222,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2159,59 +2244,63 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>479800</v>
+      </c>
+      <c r="E41" s="3">
         <v>204900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>125400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>805900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>995700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1375800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>582900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>448400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>454600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>447000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>321900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>42900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>313800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>733500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>540700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>428500</v>
       </c>
-      <c r="S41" s="3"/>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T41" s="3"/>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2260,366 +2349,390 @@
       <c r="R42" s="3">
         <v>0</v>
       </c>
-      <c r="S42" s="3"/>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3"/>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2211200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1942400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2130200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1769900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1664500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1716500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1386600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1631800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1521600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1306300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1021900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>964600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>974900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>794300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1018600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1089100</v>
       </c>
-      <c r="S43" s="3"/>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T43" s="3"/>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2375000</v>
+      </c>
+      <c r="E44" s="3">
         <v>2265700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2131600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1865600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1550400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1411500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1505400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1249200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1227700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1198400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>979800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1301700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>960900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>822000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>937500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>786800</v>
       </c>
-      <c r="S44" s="3"/>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3"/>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E45" s="3">
         <v>114500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>93600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>90700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>71700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>58200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>60900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>78900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>66000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>88100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>93900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>142900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>134700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>203600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>197700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>150200</v>
       </c>
-      <c r="S45" s="3"/>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T45" s="3"/>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5168500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4527500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4480800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4532100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4282300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4562000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3535800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3408300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3269900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3039800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2417500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>2377100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2384300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2553400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2694500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2454600</v>
       </c>
-      <c r="S46" s="3"/>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T46" s="3"/>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>42600</v>
+      </c>
+      <c r="E47" s="3">
         <v>38400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>43300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>50700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>46800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>51200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>12600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>12900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>32600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>33900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>32400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>29900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>32500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>31600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>57700</v>
       </c>
-      <c r="S47" s="3"/>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T47" s="3"/>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1537800</v>
+      </c>
+      <c r="E48" s="3">
         <v>1473800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1333800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1063300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>827300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>812800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>728100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>573600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>481100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>469900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>452100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>475800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>405500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>362200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>369900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>388700</v>
       </c>
-      <c r="S48" s="3"/>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T48" s="3"/>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2182900</v>
+      </c>
+      <c r="E49" s="3">
         <v>2187700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2246600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1499000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1513000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1518800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1427700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1428000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1477300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1520800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1557000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1607800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1683400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1755700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1809200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1880200</v>
       </c>
-      <c r="S49" s="3"/>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T49" s="3"/>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2668,9 +2781,12 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-      <c r="S50" s="3"/>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3"/>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2719,60 +2835,66 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-      <c r="S51" s="3"/>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3"/>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>94100</v>
+        <v>94600</v>
       </c>
       <c r="E52" s="3">
+        <v>85100</v>
+      </c>
+      <c r="F52" s="3">
         <v>52000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>29900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>32100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>30700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>37400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>53300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>76300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>83600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>61900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>42600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>45700</v>
       </c>
-      <c r="S52" s="3"/>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T52" s="3"/>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2821,60 +2943,66 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-      <c r="S53" s="3"/>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3"/>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10072400</v>
+      </c>
+      <c r="E54" s="3">
         <v>9423100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>9129200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7729000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6849700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>7035700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>5815900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5566300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>5294200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5098900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>4513800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>4552700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4586700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4765700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>4947800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>4826900</v>
       </c>
-      <c r="S54" s="3"/>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T54" s="3"/>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2894,8 +3022,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2915,314 +3044,333 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1074200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1143400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1214500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1129000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>747400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>860400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>577800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>795500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>776900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>651000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>466100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>552800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>586700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>531700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>683300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>768900</v>
       </c>
-      <c r="S57" s="3"/>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T57" s="3"/>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>59500</v>
+      </c>
+      <c r="E58" s="3">
         <v>419000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>229000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>64200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>51100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>46200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>52300</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>23000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>20000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>83500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>20000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>65000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>40100</v>
       </c>
-      <c r="S58" s="3"/>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T58" s="3"/>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1312300</v>
+      </c>
+      <c r="E59" s="3">
         <v>1178700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1403600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1115900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1226100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1030000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>804200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>762800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>720700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1009100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>881500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>898700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>704900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>784000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1021200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>882800</v>
       </c>
-      <c r="S59" s="3"/>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T59" s="3"/>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2664400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2987300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3089600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2428600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2143000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2151700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1585100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1741900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1690100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1683100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1367600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1458100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1311600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1380700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1704500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1691800</v>
       </c>
-      <c r="S60" s="3"/>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T60" s="3"/>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1318500</v>
+      </c>
+      <c r="E61" s="3">
         <v>809300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>819500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>788400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1009200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>995200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>936700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>819000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>818000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>807900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>826200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>844300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>875000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>890000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>955000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1020000</v>
       </c>
-      <c r="S61" s="3"/>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3"/>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>225500</v>
+      </c>
+      <c r="E62" s="3">
         <v>220400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>228800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>239000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>231300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>355900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>164500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>167300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>119700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>300500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>343500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>339200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>415100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>387200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>434800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>518500</v>
       </c>
-      <c r="S62" s="3"/>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T62" s="3"/>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3271,9 +3419,12 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-      <c r="S63" s="3"/>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3"/>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3322,9 +3473,12 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-      <c r="S64" s="3"/>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3"/>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3373,60 +3527,66 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-      <c r="S65" s="3"/>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3"/>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5541900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5271000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5423900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>4543300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3645400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>3678000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2965200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2966500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2780700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2791500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2537300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2641600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2601700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2657900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3094300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3230400</v>
       </c>
-      <c r="S66" s="3"/>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T66" s="3"/>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3446,8 +3606,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3496,9 +3657,12 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-      <c r="S68" s="3"/>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3"/>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3547,9 +3711,12 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-      <c r="S69" s="3"/>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3"/>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3598,9 +3765,12 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-      <c r="S70" s="3"/>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3"/>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3649,60 +3819,66 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-      <c r="S71" s="3"/>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3"/>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4883800</v>
+      </c>
+      <c r="E72" s="3">
         <v>4367200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3805800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3315000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3238500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3239200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2747700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2505000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2007900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2399800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2177000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2016500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1840100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1581500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1263500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1032700</v>
       </c>
-      <c r="S72" s="3"/>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T72" s="3"/>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3751,9 +3927,12 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-      <c r="S73" s="3"/>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3"/>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3802,9 +3981,12 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-      <c r="S74" s="3"/>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3"/>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3853,60 +4035,66 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-      <c r="S75" s="3"/>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3"/>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4530500</v>
+      </c>
+      <c r="E76" s="3">
         <v>4152100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3705300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>3185700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3204300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3357700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>2850700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>2599800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>2513500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>2307400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1976500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1911100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1985000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2107800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1853500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1596500</v>
       </c>
-      <c r="S76" s="3"/>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T76" s="3"/>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3955,116 +4143,125 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-      <c r="S77" s="3"/>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3"/>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44104</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43738</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43373</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43008</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42643</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42277</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41912</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41547</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>41182</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>40816</v>
       </c>
-      <c r="S80" s="2"/>
-    </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T80" s="2"/>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E81" s="3">
         <v>681400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>598000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>173900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>427400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>508900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>321500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>579400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>471900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>285600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>216400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>229000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>308100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>316000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>230200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>273000</v>
       </c>
-      <c r="S81" s="3"/>
-    </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T81" s="3"/>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4084,59 +4281,63 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>164400</v>
+      </c>
+      <c r="E83" s="3">
         <v>135200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>118200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>96000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>92500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>90800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>86300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>76700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>79800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>130300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>128800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>124500</v>
-      </c>
-      <c r="O83" s="3">
-        <v>126800</v>
       </c>
       <c r="P83" s="3">
         <v>126800</v>
       </c>
       <c r="Q83" s="3">
+        <v>126800</v>
+      </c>
+      <c r="R83" s="3">
         <v>130900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>144400</v>
       </c>
-      <c r="S83" s="3"/>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3"/>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4185,9 +4386,12 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-      <c r="S84" s="3"/>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3"/>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4236,9 +4440,12 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-      <c r="S85" s="3"/>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3"/>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4287,9 +4494,12 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-      <c r="S86" s="3"/>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3"/>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4338,9 +4548,12 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-      <c r="S87" s="3"/>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3"/>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4389,60 +4602,66 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-      <c r="S88" s="3"/>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3"/>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>783400</v>
+      </c>
+      <c r="E89" s="3">
         <v>550100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>599600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>601300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>690400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1221600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>327300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>568300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>436300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>246500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>583900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>82500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>170400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>438000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>268300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>387700</v>
       </c>
-      <c r="S89" s="3"/>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3"/>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4462,59 +4681,63 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-281000</v>
+        <v>-211800</v>
       </c>
       <c r="E91" s="3">
-        <v>-325300</v>
+        <v>-288300</v>
       </c>
       <c r="F91" s="3">
+        <v>-329900</v>
+      </c>
+      <c r="G91" s="3">
         <v>-269500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-39400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-104400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-130200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-174200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-100100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-113200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-127300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-158000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-124900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-59900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-64300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-86200</v>
       </c>
-      <c r="S91" s="3"/>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3"/>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4563,9 +4786,12 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-      <c r="S92" s="3"/>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3"/>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4614,60 +4840,66 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-      <c r="S93" s="3"/>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3"/>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-204900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-388800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1285600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-300400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-28700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-245600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-77600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-153000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-90400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-65200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-89200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-140100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-114800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-74800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-41800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-68300</v>
       </c>
-      <c r="S94" s="3"/>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3"/>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4687,59 +4919,63 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>130400</v>
+      </c>
+      <c r="E96" s="3">
         <v>120000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>107200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>97300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>24900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>90400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>81800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>75500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>71200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-62800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-55900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-53100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-50700</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
-      </c>
       <c r="Q96" s="3">
         <v>0</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
-      <c r="S96" s="3"/>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3"/>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4788,9 +5024,12 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-      <c r="S97" s="3"/>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3"/>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4839,9 +5078,12 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-      <c r="S98" s="3"/>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3"/>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4890,160 +5132,172 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-      <c r="S99" s="3"/>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3"/>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-315900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-75100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-485000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-186300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-180400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-115500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-421600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-338900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-44800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-222000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-212900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-476000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-170000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-117300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-231500</v>
       </c>
-      <c r="S100" s="3"/>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3"/>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>1600</v>
       </c>
-      <c r="S101" s="3"/>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3"/>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>274900</v>
+      </c>
+      <c r="E102" s="3">
         <v>79500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-680500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-189800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>473400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>792900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>134500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>125100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>279000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-270900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-419700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>192800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>112200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>89500</v>
       </c>
-      <c r="S102" s="3"/>
+      <c r="T102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
